--- a/output/mic.xlsx
+++ b/output/mic.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="13" count="13">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="12" count="12">
   <x:si>
     <x:t>AD</x:t>
   </x:si>
@@ -31,25 +31,22 @@
     <x:t>price</x:t>
   </x:si>
   <x:si>
-    <x:t>9863025000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cmfb001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>p1kc011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>p1nb008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>be2191</x:t>
-  </x:si>
-  <x:si>
-    <x:t>be2693</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bw6001</x:t>
+    <x:t>54877</x:t>
+  </x:si>
+  <x:si>
+    <x:t>czc003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>czc013e</x:t>
+  </x:si>
+  <x:si>
+    <x:t>kp3075</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mk1309</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mk1418</x:t>
   </x:si>
   <x:si>
     <x:t>sg2792</x:t>
@@ -437,13 +434,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C2" s="0" t="n">
-        <x:v>236</x:v>
+        <x:v>1606.5</x:v>
       </x:c>
       <x:c r="D2" s="0" t="n">
-        <x:v>236</x:v>
+        <x:v>1606.5</x:v>
       </x:c>
       <x:c r="E2" s="0" t="n">
-        <x:v>118</x:v>
+        <x:v>803.25</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
@@ -451,16 +448,16 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B3" s="0" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C3" s="0" t="n">
-        <x:v>505</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="D3" s="0" t="n">
-        <x:v>505</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="E3" s="0" t="n">
-        <x:v>505</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
@@ -468,16 +465,16 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B4" s="0" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C4" s="0" t="n">
-        <x:v>22</x:v>
+        <x:v>824</x:v>
       </x:c>
       <x:c r="D4" s="0" t="n">
-        <x:v>22</x:v>
+        <x:v>824</x:v>
       </x:c>
       <x:c r="E4" s="0" t="n">
-        <x:v>22</x:v>
+        <x:v>206</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
@@ -488,98 +485,64 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C5" s="0" t="n">
-        <x:v>105</x:v>
+        <x:v>4342.46</x:v>
       </x:c>
       <x:c r="D5" s="0" t="n">
-        <x:v>105</x:v>
+        <x:v>4342.46</x:v>
       </x:c>
       <x:c r="E5" s="0" t="n">
-        <x:v>105</x:v>
+        <x:v>4342.46</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B6" s="0" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C6" s="0" t="n">
-        <x:v>105</x:v>
+        <x:v>8068.9</x:v>
       </x:c>
       <x:c r="D6" s="0" t="n">
-        <x:v>105</x:v>
+        <x:v>8068.9</x:v>
       </x:c>
       <x:c r="E6" s="0" t="n">
-        <x:v>105</x:v>
+        <x:v>8068.9</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B7" s="0" t="n">
-        <x:v>30</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C7" s="0" t="n">
-        <x:v>233.4</x:v>
+        <x:v>7121.09</x:v>
       </x:c>
       <x:c r="D7" s="0" t="n">
-        <x:v>233.4</x:v>
+        <x:v>7121.09</x:v>
       </x:c>
       <x:c r="E7" s="0" t="n">
-        <x:v>7.78</x:v>
+        <x:v>7121.09</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B8" s="0" t="n">
-        <x:v>10</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C8" s="0" t="n">
-        <x:v>103.7</x:v>
+        <x:v>3231.36</x:v>
       </x:c>
       <x:c r="D8" s="0" t="n">
-        <x:v>103.7</x:v>
+        <x:v>3231.36</x:v>
       </x:c>
       <x:c r="E8" s="0" t="n">
-        <x:v>10.370000000000001</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:5">
-      <x:c r="A9" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="n">
-        <x:v>183.17</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="n">
-        <x:v>183.17</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="n">
-        <x:v>183.17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:5">
-      <x:c r="A10" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="n">
-        <x:v>3046.46</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="n">
-        <x:v>3046.46</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="n">
-        <x:v>1523.23</x:v>
+        <x:v>1615.68</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/output/mic.xlsx
+++ b/output/mic.xlsx
@@ -31,25 +31,25 @@
     <x:t>price</x:t>
   </x:si>
   <x:si>
-    <x:t>54877</x:t>
-  </x:si>
-  <x:si>
-    <x:t>czc003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>czc013e</x:t>
-  </x:si>
-  <x:si>
-    <x:t>kp3075</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mk1309</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mk1418</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sg2792</x:t>
+    <x:t>18900</x:t>
+  </x:si>
+  <x:si>
+    <x:t>42058050</x:t>
+  </x:si>
+  <x:si>
+    <x:t>gm1648</x:t>
+  </x:si>
+  <x:si>
+    <x:t>gs5282</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sg4878</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sg4879</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sg6320</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -431,16 +431,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B2" s="0" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C2" s="0" t="n">
-        <x:v>1606.5</x:v>
+        <x:v>695</x:v>
       </x:c>
       <x:c r="D2" s="0" t="n">
-        <x:v>1606.5</x:v>
+        <x:v>695</x:v>
       </x:c>
       <x:c r="E2" s="0" t="n">
-        <x:v>803.25</x:v>
+        <x:v>695</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
@@ -448,16 +448,16 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B3" s="0" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C3" s="0" t="n">
-        <x:v>544</x:v>
+        <x:v>1420</x:v>
       </x:c>
       <x:c r="D3" s="0" t="n">
-        <x:v>544</x:v>
+        <x:v>1420</x:v>
       </x:c>
       <x:c r="E3" s="0" t="n">
-        <x:v>136</x:v>
+        <x:v>1420</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
@@ -465,16 +465,16 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B4" s="0" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C4" s="0" t="n">
-        <x:v>824</x:v>
+        <x:v>428.54</x:v>
       </x:c>
       <x:c r="D4" s="0" t="n">
-        <x:v>824</x:v>
+        <x:v>428.54</x:v>
       </x:c>
       <x:c r="E4" s="0" t="n">
-        <x:v>206</x:v>
+        <x:v>214.27</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
@@ -485,13 +485,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C5" s="0" t="n">
-        <x:v>4342.46</x:v>
+        <x:v>2582.5</x:v>
       </x:c>
       <x:c r="D5" s="0" t="n">
-        <x:v>4342.46</x:v>
+        <x:v>2582.5</x:v>
       </x:c>
       <x:c r="E5" s="0" t="n">
-        <x:v>4342.46</x:v>
+        <x:v>2582.5</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
@@ -502,13 +502,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C6" s="0" t="n">
-        <x:v>8068.9</x:v>
+        <x:v>2462.4</x:v>
       </x:c>
       <x:c r="D6" s="0" t="n">
-        <x:v>8068.9</x:v>
+        <x:v>2462.4</x:v>
       </x:c>
       <x:c r="E6" s="0" t="n">
-        <x:v>8068.9</x:v>
+        <x:v>2462.4</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
@@ -519,13 +519,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C7" s="0" t="n">
-        <x:v>7121.09</x:v>
+        <x:v>2462.4</x:v>
       </x:c>
       <x:c r="D7" s="0" t="n">
-        <x:v>7121.09</x:v>
+        <x:v>2462.4</x:v>
       </x:c>
       <x:c r="E7" s="0" t="n">
-        <x:v>7121.09</x:v>
+        <x:v>2462.4</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
@@ -533,16 +533,16 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B8" s="0" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C8" s="0" t="n">
-        <x:v>3231.36</x:v>
+        <x:v>2902.18</x:v>
       </x:c>
       <x:c r="D8" s="0" t="n">
-        <x:v>3231.36</x:v>
+        <x:v>2902.18</x:v>
       </x:c>
       <x:c r="E8" s="0" t="n">
-        <x:v>1615.68</x:v>
+        <x:v>2902.18</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
